--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L707"/>
+  <dimension ref="A1:L712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30073,7 +30073,7 @@
         <v>661.21</v>
       </c>
       <c r="K706" t="n">
-        <v>727.84</v>
+        <v>767.33</v>
       </c>
       <c r="L706" t="inlineStr">
         <is>
@@ -30112,12 +30112,222 @@
         <v>198.73</v>
       </c>
       <c r="J707" t="n">
-        <v>669.3</v>
+        <v>661.21</v>
       </c>
       <c r="K707" t="n">
-        <v>693.09</v>
+        <v>767.33</v>
       </c>
       <c r="L707" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="n">
+        <v>643.5599999999999</v>
+      </c>
+      <c r="C708" t="n">
+        <v>658.76</v>
+      </c>
+      <c r="D708" t="n">
+        <v>189.02</v>
+      </c>
+      <c r="E708" t="n">
+        <v>188.44</v>
+      </c>
+      <c r="F708" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="G708" t="n">
+        <v>215.95</v>
+      </c>
+      <c r="H708" t="n">
+        <v>173.44</v>
+      </c>
+      <c r="I708" t="n">
+        <v>196.09</v>
+      </c>
+      <c r="J708" t="n">
+        <v>666.96</v>
+      </c>
+      <c r="K708" t="n">
+        <v>767.11</v>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="n">
+        <v>643.13</v>
+      </c>
+      <c r="C709" t="n">
+        <v>658.15</v>
+      </c>
+      <c r="D709" t="n">
+        <v>188</v>
+      </c>
+      <c r="E709" t="n">
+        <v>186.4</v>
+      </c>
+      <c r="F709" t="n">
+        <v>204.15</v>
+      </c>
+      <c r="G709" t="n">
+        <v>214.99</v>
+      </c>
+      <c r="H709" t="n">
+        <v>172.57</v>
+      </c>
+      <c r="I709" t="n">
+        <v>196.15</v>
+      </c>
+      <c r="J709" t="n">
+        <v>673.53</v>
+      </c>
+      <c r="K709" t="n">
+        <v>766.61</v>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="n">
+        <v>641.4299999999999</v>
+      </c>
+      <c r="C710" t="n">
+        <v>657.05</v>
+      </c>
+      <c r="D710" t="n">
+        <v>186</v>
+      </c>
+      <c r="E710" t="n">
+        <v>182.9</v>
+      </c>
+      <c r="F710" t="n">
+        <v>203.54</v>
+      </c>
+      <c r="G710" t="n">
+        <v>213.01</v>
+      </c>
+      <c r="H710" t="n">
+        <v>169.23</v>
+      </c>
+      <c r="I710" t="n">
+        <v>195.2</v>
+      </c>
+      <c r="J710" t="n">
+        <v>674.62</v>
+      </c>
+      <c r="K710" t="n">
+        <v>722.65</v>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="n">
+        <v>641.41</v>
+      </c>
+      <c r="C711" t="n">
+        <v>657.13</v>
+      </c>
+      <c r="D711" t="n">
+        <v>184.77</v>
+      </c>
+      <c r="E711" t="n">
+        <v>181.93</v>
+      </c>
+      <c r="F711" t="n">
+        <v>199.34</v>
+      </c>
+      <c r="G711" t="n">
+        <v>212.51</v>
+      </c>
+      <c r="H711" t="n">
+        <v>168.92</v>
+      </c>
+      <c r="I711" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="J711" t="n">
+        <v>682.75</v>
+      </c>
+      <c r="K711" t="n">
+        <v>686.33</v>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="n">
+        <v>640.4299999999999</v>
+      </c>
+      <c r="C712" t="n">
+        <v>656.01</v>
+      </c>
+      <c r="D712" t="n">
+        <v>183.07</v>
+      </c>
+      <c r="E712" t="n">
+        <v>180.42</v>
+      </c>
+      <c r="F712" t="n">
+        <v>195.53</v>
+      </c>
+      <c r="G712" t="n">
+        <v>211.51</v>
+      </c>
+      <c r="H712" t="n">
+        <v>167.44</v>
+      </c>
+      <c r="I712" t="n">
+        <v>194.95</v>
+      </c>
+      <c r="J712" t="n">
+        <v>689.33</v>
+      </c>
+      <c r="K712" t="n">
+        <v>654.9299999999999</v>
+      </c>
+      <c r="L712" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30134,7 +30344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B754"/>
+  <dimension ref="A1:B759"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37677,6 +37887,56 @@
       </c>
       <c r="B754" t="n">
         <v>-0.25</v>
+      </c>
+    </row>
+    <row r="755">
+      <c r="A755" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B755" t="n">
+        <v>0.02</v>
+      </c>
+    </row>
+    <row r="756">
+      <c r="A756" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B756" t="n">
+        <v>0.26</v>
+      </c>
+    </row>
+    <row r="757">
+      <c r="A757" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B757" t="n">
+        <v>-0.43</v>
+      </c>
+    </row>
+    <row r="758">
+      <c r="A758" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B758" t="n">
+        <v>0.78</v>
+      </c>
+    </row>
+    <row r="759">
+      <c r="A759" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B759" t="n">
+        <v>-0.77</v>
       </c>
     </row>
   </sheetData>
@@ -37839,28 +38099,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02464732560494132</v>
+        <v>-0.02945393346301751</v>
       </c>
       <c r="J2" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K2" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001211773682022299</v>
+        <v>0.001750706489024312</v>
       </c>
       <c r="M2" t="n">
-        <v>4.572975793130293</v>
+        <v>4.565318608650441</v>
       </c>
       <c r="N2" t="n">
-        <v>29.21885602497549</v>
+        <v>29.11001813020836</v>
       </c>
       <c r="O2" t="n">
-        <v>5.405446884853785</v>
+        <v>5.395370064250307</v>
       </c>
       <c r="P2" t="n">
-        <v>646.2143054739793</v>
+        <v>646.264184341944</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -37911,28 +38171,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.115914649062423</v>
+        <v>-0.1161446887064549</v>
       </c>
       <c r="J3" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K3" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01553589779330011</v>
+        <v>0.01583406473726956</v>
       </c>
       <c r="M3" t="n">
-        <v>4.641739281779324</v>
+        <v>4.615254319872218</v>
       </c>
       <c r="N3" t="n">
-        <v>49.68346583578778</v>
+        <v>49.34064521026739</v>
       </c>
       <c r="O3" t="n">
-        <v>7.048649930007007</v>
+        <v>7.024289658767453</v>
       </c>
       <c r="P3" t="n">
-        <v>660.7034203609885</v>
+        <v>660.7058210239562</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -37983,28 +38243,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5144681838269389</v>
+        <v>-0.5240260031956836</v>
       </c>
       <c r="J4" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K4" t="n">
-        <v>703</v>
+        <v>708</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04690288701139389</v>
+        <v>0.04924288547970601</v>
       </c>
       <c r="M4" t="n">
-        <v>14.85647666630881</v>
+        <v>14.80247280082674</v>
       </c>
       <c r="N4" t="n">
-        <v>311.3558571778655</v>
+        <v>309.5294442651818</v>
       </c>
       <c r="O4" t="n">
-        <v>17.64527860867789</v>
+        <v>17.59344890194023</v>
       </c>
       <c r="P4" t="n">
-        <v>207.0223858424321</v>
+        <v>207.1222230215946</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38055,28 +38315,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.272816966389095</v>
+        <v>-0.2805933734770282</v>
       </c>
       <c r="J5" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K5" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0279074726995383</v>
+        <v>0.02986392440886187</v>
       </c>
       <c r="M5" t="n">
-        <v>10.81658792565433</v>
+        <v>10.78143340036784</v>
       </c>
       <c r="N5" t="n">
-        <v>151.2869795846251</v>
+        <v>150.5118871250117</v>
       </c>
       <c r="O5" t="n">
-        <v>12.29987721827438</v>
+        <v>12.26832861986553</v>
       </c>
       <c r="P5" t="n">
-        <v>197.1039941589441</v>
+        <v>197.184706704709</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38127,28 +38387,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2391316582221036</v>
+        <v>0.2383957118870688</v>
       </c>
       <c r="J6" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K6" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02015929581485987</v>
+        <v>0.02033349827476927</v>
       </c>
       <c r="M6" t="n">
-        <v>10.47285240331389</v>
+        <v>10.42096070043604</v>
       </c>
       <c r="N6" t="n">
-        <v>162.2978338872244</v>
+        <v>161.2394670265486</v>
       </c>
       <c r="O6" t="n">
-        <v>12.73961670880346</v>
+        <v>12.69801035700273</v>
       </c>
       <c r="P6" t="n">
-        <v>195.4518492516771</v>
+        <v>195.4595379998399</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38199,28 +38459,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>0.002071249702023264</v>
+        <v>-0.002459061289157541</v>
       </c>
       <c r="J7" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K7" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="L7" t="n">
-        <v>5.195942018310085e-06</v>
+        <v>7.423090464864224e-06</v>
       </c>
       <c r="M7" t="n">
-        <v>5.954828369218422</v>
+        <v>5.935933698023161</v>
       </c>
       <c r="N7" t="n">
-        <v>48.21218549123702</v>
+        <v>47.96882156621778</v>
       </c>
       <c r="O7" t="n">
-        <v>6.943499513302857</v>
+        <v>6.925952755124582</v>
       </c>
       <c r="P7" t="n">
-        <v>216.8913024209824</v>
+        <v>216.9383266806441</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38271,28 +38531,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1169771882663382</v>
+        <v>0.1031542953574793</v>
       </c>
       <c r="J8" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K8" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="L8" t="n">
-        <v>0.00423226693715173</v>
+        <v>0.003332103102082873</v>
       </c>
       <c r="M8" t="n">
-        <v>11.10822024237229</v>
+        <v>11.10437506701109</v>
       </c>
       <c r="N8" t="n">
-        <v>187.0381902858946</v>
+        <v>186.4734461419025</v>
       </c>
       <c r="O8" t="n">
-        <v>13.67619063503776</v>
+        <v>13.65552804332013</v>
       </c>
       <c r="P8" t="n">
-        <v>177.3692951273795</v>
+        <v>177.5132026092802</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38343,28 +38603,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2197534529603881</v>
+        <v>-0.2288243522564243</v>
       </c>
       <c r="J9" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K9" t="n">
-        <v>705</v>
+        <v>710</v>
       </c>
       <c r="L9" t="n">
-        <v>0.04970366285123418</v>
+        <v>0.05416180078917021</v>
       </c>
       <c r="M9" t="n">
-        <v>5.706813490729895</v>
+        <v>5.714635812129742</v>
       </c>
       <c r="N9" t="n">
-        <v>53.63953620041036</v>
+        <v>53.57208659725168</v>
       </c>
       <c r="O9" t="n">
-        <v>7.323901706086065</v>
+        <v>7.319295498697376</v>
       </c>
       <c r="P9" t="n">
-        <v>208.0674776833432</v>
+        <v>208.1618980955946</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38415,28 +38675,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.466025420301135</v>
+        <v>2.449575027574512</v>
       </c>
       <c r="J10" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K10" t="n">
-        <v>702</v>
+        <v>707</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1288673153780757</v>
+        <v>0.1290268609845096</v>
       </c>
       <c r="M10" t="n">
-        <v>28.80090321745245</v>
+        <v>28.65672793852123</v>
       </c>
       <c r="N10" t="n">
-        <v>2380.659442263828</v>
+        <v>2365.515719574153</v>
       </c>
       <c r="O10" t="n">
-        <v>48.79200182677308</v>
+        <v>48.63656771991783</v>
       </c>
       <c r="P10" t="n">
-        <v>621.6475889442395</v>
+        <v>621.819226690295</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38487,28 +38747,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6325857841146957</v>
+        <v>0.6930744513831172</v>
       </c>
       <c r="J11" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="K11" t="n">
-        <v>706</v>
+        <v>711</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00144541799212039</v>
+        <v>0.001758346287631496</v>
       </c>
       <c r="M11" t="n">
-        <v>101.4741652734084</v>
+        <v>101.1039857981839</v>
       </c>
       <c r="N11" t="n">
-        <v>16132.02601700267</v>
+        <v>16048.01278635637</v>
       </c>
       <c r="O11" t="n">
-        <v>127.0119128940379</v>
+        <v>126.6807514437626</v>
       </c>
       <c r="P11" t="n">
-        <v>680.206150369195</v>
+        <v>679.5804814842629</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38546,7 +38806,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L707"/>
+  <dimension ref="A1:L712"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82339,6 +82599,316 @@
         </is>
       </c>
     </row>
+    <row r="708">
+      <c r="A708" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-03 22:13:19+00:00</t>
+        </is>
+      </c>
+      <c r="B708" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C708" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D708" t="inlineStr">
+        <is>
+          <t>-43.63038513932523,172.6958524645721</t>
+        </is>
+      </c>
+      <c r="E708" t="inlineStr">
+        <is>
+          <t>-43.63037992014856,172.6948607788642</t>
+        </is>
+      </c>
+      <c r="F708" t="inlineStr">
+        <is>
+          <t>-43.630521367965365,172.69386910115836</t>
+        </is>
+      </c>
+      <c r="G708" t="inlineStr">
+        <is>
+          <t>-43.63055315143244,172.69286030619324</t>
+        </is>
+      </c>
+      <c r="H708" t="inlineStr">
+        <is>
+          <t>-43.63028089725619,172.69178781966474</t>
+        </is>
+      </c>
+      <c r="I708" t="inlineStr">
+        <is>
+          <t>-43.63079610592385,172.6910399707308</t>
+        </is>
+      </c>
+      <c r="J708" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K708" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L708" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="709">
+      <c r="A709" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-04 22:07:01+00:00</t>
+        </is>
+      </c>
+      <c r="B709" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C709" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D709" t="inlineStr">
+        <is>
+          <t>-43.63037595521696,172.69585246378276</t>
+        </is>
+      </c>
+      <c r="E709" t="inlineStr">
+        <is>
+          <t>-43.63036155193287,172.6948607775875</t>
+        </is>
+      </c>
+      <c r="F709" t="inlineStr">
+        <is>
+          <t>-43.630521367965365,172.69386910115836</t>
+        </is>
+      </c>
+      <c r="G709" t="inlineStr">
+        <is>
+          <t>-43.63054456627851,172.6928616908398</t>
+        </is>
+      </c>
+      <c r="H709" t="inlineStr">
+        <is>
+          <t>-43.630273959311175,172.69178281235307</t>
+        </is>
+      </c>
+      <c r="I709" t="inlineStr">
+        <is>
+          <t>-43.630796584432304,172.69104031598795</t>
+        </is>
+      </c>
+      <c r="J709" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K709" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L709" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="710">
+      <c r="A710" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-11 22:13:13+00:00</t>
+        </is>
+      </c>
+      <c r="B710" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C710" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D710" t="inlineStr">
+        <is>
+          <t>-43.63035794716148,172.695852462235</t>
+        </is>
+      </c>
+      <c r="E710" t="inlineStr">
+        <is>
+          <t>-43.630330037837176,172.69486077539702</t>
+        </is>
+      </c>
+      <c r="F710" t="inlineStr">
+        <is>
+          <t>-43.63051587550912,172.69386910086698</t>
+        </is>
+      </c>
+      <c r="G710" t="inlineStr">
+        <is>
+          <t>-43.63052685939843,172.69286454667207</t>
+        </is>
+      </c>
+      <c r="H710" t="inlineStr">
+        <is>
+          <t>-43.630247323979916,172.69176358889135</t>
+        </is>
+      </c>
+      <c r="I710" t="inlineStr">
+        <is>
+          <t>-43.63078900804809,172.69103484941706</t>
+        </is>
+      </c>
+      <c r="J710" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K710" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L710" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="711">
+      <c r="A711" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-19 22:13:28+00:00</t>
+        </is>
+      </c>
+      <c r="B711" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C711" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D711" t="inlineStr">
+        <is>
+          <t>-43.630346872207326,172.6958524612831</t>
+        </is>
+      </c>
+      <c r="E711" t="inlineStr">
+        <is>
+          <t>-43.63032130393063,172.6948607747899</t>
+        </is>
+      </c>
+      <c r="F711" t="inlineStr">
+        <is>
+          <t>-43.63047805859712,172.6938690988607</t>
+        </is>
+      </c>
+      <c r="G711" t="inlineStr">
+        <is>
+          <t>-43.63052238796405,172.69286526784157</t>
+        </is>
+      </c>
+      <c r="H711" t="inlineStr">
+        <is>
+          <t>-43.63024485183823,172.6917618046787</t>
+        </is>
+      </c>
+      <c r="I711" t="inlineStr">
+        <is>
+          <t>-43.63078701426273,172.691033410846</t>
+        </is>
+      </c>
+      <c r="J711" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K711" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L711" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="712">
+      <c r="A712" s="1" t="inlineStr">
+        <is>
+          <t>2026-07-28 22:07:23+00:00</t>
+        </is>
+      </c>
+      <c r="B712" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C712" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D712" t="inlineStr">
+        <is>
+          <t>-43.630331565360116,172.69585245996748</t>
+        </is>
+      </c>
+      <c r="E712" t="inlineStr">
+        <is>
+          <t>-43.63030770784927,172.69486077384482</t>
+        </is>
+      </c>
+      <c r="F712" t="inlineStr">
+        <is>
+          <t>-43.630443753255285,172.6938690970406</t>
+        </is>
+      </c>
+      <c r="G712" t="inlineStr">
+        <is>
+          <t>-43.63051344509524,172.69286671018023</t>
+        </is>
+      </c>
+      <c r="H712" t="inlineStr">
+        <is>
+          <t>-43.63023304935491,172.69175328650417</t>
+        </is>
+      </c>
+      <c r="I712" t="inlineStr">
+        <is>
+          <t>-43.63078701426273,172.691033410846</t>
+        </is>
+      </c>
+      <c r="J712" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K712" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L712"/>
+  <dimension ref="A1:L714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30319,7 +30319,7 @@
         <v>167.44</v>
       </c>
       <c r="I712" t="n">
-        <v>194.95</v>
+        <v>197.45</v>
       </c>
       <c r="J712" t="n">
         <v>689.33</v>
@@ -30328,6 +30328,90 @@
         <v>654.9299999999999</v>
       </c>
       <c r="L712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="n">
+        <v>640.04</v>
+      </c>
+      <c r="C713" t="n">
+        <v>656.28</v>
+      </c>
+      <c r="D713" t="n">
+        <v>180.95</v>
+      </c>
+      <c r="E713" t="n">
+        <v>177.92</v>
+      </c>
+      <c r="F713" t="n">
+        <v>192.26</v>
+      </c>
+      <c r="G713" t="n">
+        <v>210.5</v>
+      </c>
+      <c r="H713" t="n">
+        <v>166.27</v>
+      </c>
+      <c r="I713" t="n">
+        <v>197.44</v>
+      </c>
+      <c r="J713" t="n">
+        <v>693.88</v>
+      </c>
+      <c r="K713" t="n">
+        <v>627.46</v>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="n">
+        <v>639.75</v>
+      </c>
+      <c r="C714" t="n">
+        <v>655.8099999999999</v>
+      </c>
+      <c r="D714" t="n">
+        <v>179.54</v>
+      </c>
+      <c r="E714" t="n">
+        <v>175.05</v>
+      </c>
+      <c r="F714" t="n">
+        <v>189.52</v>
+      </c>
+      <c r="G714" t="n">
+        <v>209.66</v>
+      </c>
+      <c r="H714" t="n">
+        <v>166.13</v>
+      </c>
+      <c r="I714" t="n">
+        <v>197.68</v>
+      </c>
+      <c r="J714" t="n">
+        <v>698.28</v>
+      </c>
+      <c r="K714" t="n">
+        <v>619.97</v>
+      </c>
+      <c r="L714" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30344,7 +30428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B759"/>
+  <dimension ref="A1:B761"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -37937,6 +38021,26 @@
       </c>
       <c r="B759" t="n">
         <v>-0.77</v>
+      </c>
+    </row>
+    <row r="760">
+      <c r="A760" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B760" t="n">
+        <v>0.87</v>
+      </c>
+    </row>
+    <row r="761">
+      <c r="A761" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B761" t="n">
+        <v>0.68</v>
       </c>
     </row>
   </sheetData>
@@ -38099,28 +38203,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.02945393346301751</v>
+        <v>-0.03246027390588091</v>
       </c>
       <c r="J2" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K2" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L2" t="n">
-        <v>0.001750706489024312</v>
+        <v>0.002132291829749833</v>
       </c>
       <c r="M2" t="n">
-        <v>4.565318608650441</v>
+        <v>4.567753717587759</v>
       </c>
       <c r="N2" t="n">
-        <v>29.11001813020836</v>
+        <v>29.11483703894661</v>
       </c>
       <c r="O2" t="n">
-        <v>5.395370064250307</v>
+        <v>5.395816623917701</v>
       </c>
       <c r="P2" t="n">
-        <v>646.264184341944</v>
+        <v>646.2954861619213</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38171,28 +38275,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1161446887064549</v>
+        <v>-0.1169685341042409</v>
       </c>
       <c r="J3" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K3" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01583406473726956</v>
+        <v>0.01615126878682727</v>
       </c>
       <c r="M3" t="n">
-        <v>4.615254319872218</v>
+        <v>4.606904118561983</v>
       </c>
       <c r="N3" t="n">
-        <v>49.34064521026739</v>
+        <v>49.20887733479632</v>
       </c>
       <c r="O3" t="n">
-        <v>7.024289658767453</v>
+        <v>7.014903943376297</v>
       </c>
       <c r="P3" t="n">
-        <v>660.7058210239562</v>
+        <v>660.7143998190629</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38243,28 +38347,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5240260031956836</v>
+        <v>-0.5309529634767159</v>
       </c>
       <c r="J4" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K4" t="n">
-        <v>708</v>
+        <v>710</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04924288547970601</v>
+        <v>0.05071312820950069</v>
       </c>
       <c r="M4" t="n">
-        <v>14.80247280082674</v>
+        <v>14.79732388040597</v>
       </c>
       <c r="N4" t="n">
-        <v>309.5294442651818</v>
+        <v>309.1124721767728</v>
       </c>
       <c r="O4" t="n">
-        <v>17.59344890194023</v>
+        <v>17.58159469947971</v>
       </c>
       <c r="P4" t="n">
-        <v>207.1222230215946</v>
+        <v>207.1948231413849</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38315,28 +38419,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2805933734770282</v>
+        <v>-0.2876776073475324</v>
       </c>
       <c r="J5" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K5" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L5" t="n">
-        <v>0.02986392440886187</v>
+        <v>0.03143204484817019</v>
       </c>
       <c r="M5" t="n">
-        <v>10.78143340036784</v>
+        <v>10.78858980912223</v>
       </c>
       <c r="N5" t="n">
-        <v>150.5118871250117</v>
+        <v>150.5751326123991</v>
       </c>
       <c r="O5" t="n">
-        <v>12.26832861986553</v>
+        <v>12.27090594098085</v>
       </c>
       <c r="P5" t="n">
-        <v>197.184706704709</v>
+        <v>197.2584728448008</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38387,28 +38491,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2383957118870688</v>
+        <v>0.2324633926203691</v>
       </c>
       <c r="J6" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K6" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L6" t="n">
-        <v>0.02033349827476927</v>
+        <v>0.01943002561494012</v>
       </c>
       <c r="M6" t="n">
-        <v>10.42096070043604</v>
+        <v>10.42693102065901</v>
       </c>
       <c r="N6" t="n">
-        <v>161.2394670265486</v>
+        <v>161.1286392220799</v>
       </c>
       <c r="O6" t="n">
-        <v>12.69801035700273</v>
+        <v>12.69364562377885</v>
       </c>
       <c r="P6" t="n">
-        <v>195.4595379998399</v>
+        <v>195.5213166165802</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38459,28 +38563,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.002459061289157541</v>
+        <v>-0.006120099901009952</v>
       </c>
       <c r="J7" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K7" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L7" t="n">
-        <v>7.423090464864224e-06</v>
+        <v>4.613708477851919e-05</v>
       </c>
       <c r="M7" t="n">
-        <v>5.935933698023161</v>
+        <v>5.937877430986552</v>
       </c>
       <c r="N7" t="n">
-        <v>47.96882156621778</v>
+        <v>47.96287567294176</v>
       </c>
       <c r="O7" t="n">
-        <v>6.925952755124582</v>
+        <v>6.925523494505073</v>
       </c>
       <c r="P7" t="n">
-        <v>216.9383266806441</v>
+        <v>216.9764502245468</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38531,28 +38635,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.1031542953574793</v>
+        <v>0.09552498527015191</v>
       </c>
       <c r="J8" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K8" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L8" t="n">
-        <v>0.003332103102082873</v>
+        <v>0.002867931871854967</v>
       </c>
       <c r="M8" t="n">
-        <v>11.10437506701109</v>
+        <v>11.11392676056879</v>
       </c>
       <c r="N8" t="n">
-        <v>186.4734461419025</v>
+        <v>186.5027047614997</v>
       </c>
       <c r="O8" t="n">
-        <v>13.65552804332013</v>
+        <v>13.65659931174301</v>
       </c>
       <c r="P8" t="n">
-        <v>177.5132026092802</v>
+        <v>177.5929026053269</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38603,28 +38707,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2288243522564243</v>
+        <v>-0.2305503770984938</v>
       </c>
       <c r="J9" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K9" t="n">
-        <v>710</v>
+        <v>712</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05416180078917021</v>
+        <v>0.05524406760976686</v>
       </c>
       <c r="M9" t="n">
-        <v>5.714635812129742</v>
+        <v>5.707795302372983</v>
       </c>
       <c r="N9" t="n">
-        <v>53.57208659725168</v>
+        <v>53.4358812418188</v>
       </c>
       <c r="O9" t="n">
-        <v>7.319295498697376</v>
+        <v>7.309985037044795</v>
       </c>
       <c r="P9" t="n">
-        <v>208.1618980955946</v>
+        <v>208.179941553448</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38675,28 +38779,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.449575027574512</v>
+        <v>2.454042014400553</v>
       </c>
       <c r="J10" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K10" t="n">
-        <v>707</v>
+        <v>709</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1290268609845096</v>
+        <v>0.1301243142685252</v>
       </c>
       <c r="M10" t="n">
-        <v>28.65672793852123</v>
+        <v>28.6068684976819</v>
       </c>
       <c r="N10" t="n">
-        <v>2365.515719574153</v>
+        <v>2359.044612168486</v>
       </c>
       <c r="O10" t="n">
-        <v>48.63656771991783</v>
+        <v>48.5699970369413</v>
       </c>
       <c r="P10" t="n">
-        <v>621.819226690295</v>
+        <v>621.7723847348525</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38747,28 +38851,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.6930744513831172</v>
+        <v>0.652871181447758</v>
       </c>
       <c r="J11" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="K11" t="n">
-        <v>711</v>
+        <v>713</v>
       </c>
       <c r="L11" t="n">
-        <v>0.001758346287631496</v>
+        <v>0.00156868339271965</v>
       </c>
       <c r="M11" t="n">
-        <v>101.1039857981839</v>
+        <v>101.1005077823664</v>
       </c>
       <c r="N11" t="n">
-        <v>16048.01278635637</v>
+        <v>16018.4898586241</v>
       </c>
       <c r="O11" t="n">
-        <v>126.6807514437626</v>
+        <v>126.564172887212</v>
       </c>
       <c r="P11" t="n">
-        <v>679.5804814842629</v>
+        <v>679.9990847803964</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38806,7 +38910,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L712"/>
+  <dimension ref="A1:L714"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -82890,7 +82994,7 @@
       </c>
       <c r="I712" t="inlineStr">
         <is>
-          <t>-43.63078701426273,172.691033410846</t>
+          <t>-43.63080695211555,172.69104779656084</t>
         </is>
       </c>
       <c r="J712" t="inlineStr">
@@ -82904,6 +83008,130 @@
         </is>
       </c>
       <c r="L712" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="713">
+      <c r="A713" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-05 22:07:16+00:00</t>
+        </is>
+      </c>
+      <c r="B713" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C713" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D713" t="inlineStr">
+        <is>
+          <t>-43.63031247682117,172.69585245832675</t>
+        </is>
+      </c>
+      <c r="E713" t="inlineStr">
+        <is>
+          <t>-43.630285197780736,172.6948607722801</t>
+        </is>
+      </c>
+      <c r="F713" t="inlineStr">
+        <is>
+          <t>-43.63041431008773,172.69386909547836</t>
+        </is>
+      </c>
+      <c r="G713" t="inlineStr">
+        <is>
+          <t>-43.63050441279774,172.69286816694182</t>
+        </is>
+      </c>
+      <c r="H713" t="inlineStr">
+        <is>
+          <t>-43.63022371901292,172.6917465525442</t>
+        </is>
+      </c>
+      <c r="I713" t="inlineStr">
+        <is>
+          <t>-43.63080687236413,172.69104773901796</t>
+        </is>
+      </c>
+      <c r="J713" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K713" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L713" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="714">
+      <c r="A714" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-20 22:13:36+00:00</t>
+        </is>
+      </c>
+      <c r="B714" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C714" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D714" t="inlineStr">
+        <is>
+          <t>-43.63029978114192,172.6958524572355</t>
+        </is>
+      </c>
+      <c r="E714" t="inlineStr">
+        <is>
+          <t>-43.63025935622193,172.69486077048373</t>
+        </is>
+      </c>
+      <c r="F714" t="inlineStr">
+        <is>
+          <t>-43.63038963905425,172.6938690941693</t>
+        </is>
+      </c>
+      <c r="G714" t="inlineStr">
+        <is>
+          <t>-43.6304969007879,172.6928693785056</t>
+        </is>
+      </c>
+      <c r="H714" t="inlineStr">
+        <is>
+          <t>-43.630222602561716,172.69174574677137</t>
+        </is>
+      </c>
+      <c r="I714" t="inlineStr">
+        <is>
+          <t>-43.63080878639792,172.6910491200471</t>
+        </is>
+      </c>
+      <c r="J714" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K714" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L714" t="inlineStr">
         <is>
           <t>L9</t>
         </is>

--- a/data/nzd0580/nzd0580.xlsx
+++ b/data/nzd0580/nzd0580.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L714"/>
+  <dimension ref="A1:L717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -30409,9 +30409,135 @@
         <v>698.28</v>
       </c>
       <c r="K714" t="n">
-        <v>619.97</v>
+        <v>629.6799999999999</v>
       </c>
       <c r="L714" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="n">
+        <v>639.6</v>
+      </c>
+      <c r="C715" t="n">
+        <v>655.89</v>
+      </c>
+      <c r="D715" t="n">
+        <v>179.47</v>
+      </c>
+      <c r="E715" t="n">
+        <v>175.76</v>
+      </c>
+      <c r="F715" t="n">
+        <v>189.78</v>
+      </c>
+      <c r="G715" t="n">
+        <v>210.06</v>
+      </c>
+      <c r="H715" t="n">
+        <v>165.7</v>
+      </c>
+      <c r="I715" t="n">
+        <v>197.78</v>
+      </c>
+      <c r="J715" t="n">
+        <v>695.98</v>
+      </c>
+      <c r="K715" t="n">
+        <v>637.52</v>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="n">
+        <v>637.97</v>
+      </c>
+      <c r="C716" t="n">
+        <v>654.67</v>
+      </c>
+      <c r="D716" t="n">
+        <v>176.17</v>
+      </c>
+      <c r="E716" t="n">
+        <v>172.3</v>
+      </c>
+      <c r="F716" t="n">
+        <v>184.46</v>
+      </c>
+      <c r="G716" t="n">
+        <v>208.22</v>
+      </c>
+      <c r="H716" t="n">
+        <v>163.58</v>
+      </c>
+      <c r="I716" t="n">
+        <v>198.28</v>
+      </c>
+      <c r="J716" t="n">
+        <v>706.29</v>
+      </c>
+      <c r="K716" t="n">
+        <v>609.8099999999999</v>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="n">
+        <v>638.4</v>
+      </c>
+      <c r="C717" t="n">
+        <v>655.0700000000001</v>
+      </c>
+      <c r="D717" t="n">
+        <v>176.86</v>
+      </c>
+      <c r="E717" t="n">
+        <v>173.09</v>
+      </c>
+      <c r="F717" t="n">
+        <v>185.71</v>
+      </c>
+      <c r="G717" t="n">
+        <v>208.79</v>
+      </c>
+      <c r="H717" t="n">
+        <v>164.38</v>
+      </c>
+      <c r="I717" t="n">
+        <v>197.55</v>
+      </c>
+      <c r="J717" t="n">
+        <v>702.84</v>
+      </c>
+      <c r="K717" t="n">
+        <v>620.47</v>
+      </c>
+      <c r="L717" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -30428,7 +30554,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B761"/>
+  <dimension ref="A1:B764"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -38041,6 +38167,36 @@
       </c>
       <c r="B761" t="n">
         <v>0.68</v>
+      </c>
+    </row>
+    <row r="762">
+      <c r="A762" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B762" t="n">
+        <v>-0.77</v>
+      </c>
+    </row>
+    <row r="763">
+      <c r="A763" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B763" t="n">
+        <v>-0.29</v>
+      </c>
+    </row>
+    <row r="764">
+      <c r="A764" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B764" t="n">
+        <v>0.13</v>
       </c>
     </row>
   </sheetData>
@@ -38203,28 +38359,28 @@
         <v>0.2</v>
       </c>
       <c r="I2" t="n">
-        <v>-0.03246027390588091</v>
+        <v>-0.03788992884821982</v>
       </c>
       <c r="J2" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K2" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L2" t="n">
-        <v>0.002132291829749833</v>
+        <v>0.002910738839918547</v>
       </c>
       <c r="M2" t="n">
-        <v>4.567753717587759</v>
+        <v>4.575955297530047</v>
       </c>
       <c r="N2" t="n">
-        <v>29.11483703894661</v>
+        <v>29.18373360100678</v>
       </c>
       <c r="O2" t="n">
-        <v>5.395816623917701</v>
+        <v>5.4021971086778</v>
       </c>
       <c r="P2" t="n">
-        <v>646.2954861619213</v>
+        <v>646.3522026544741</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -38275,28 +38431,28 @@
         <v>0.2</v>
       </c>
       <c r="I3" t="n">
-        <v>-0.1169685341042409</v>
+        <v>-0.1188478466722678</v>
       </c>
       <c r="J3" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K3" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L3" t="n">
-        <v>0.01615126878682727</v>
+        <v>0.0168094263206594</v>
       </c>
       <c r="M3" t="n">
-        <v>4.606904118561983</v>
+        <v>4.598017836197277</v>
       </c>
       <c r="N3" t="n">
-        <v>49.20887733479632</v>
+        <v>49.02639094535051</v>
       </c>
       <c r="O3" t="n">
-        <v>7.014903943376297</v>
+        <v>7.001884813773397</v>
       </c>
       <c r="P3" t="n">
-        <v>660.7143998190629</v>
+        <v>660.7340324493015</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -38347,28 +38503,28 @@
         <v>0.1419</v>
       </c>
       <c r="I4" t="n">
-        <v>-0.5309529634767159</v>
+        <v>-0.5433688416873961</v>
       </c>
       <c r="J4" t="n">
+        <v>716</v>
+      </c>
+      <c r="K4" t="n">
         <v>713</v>
       </c>
-      <c r="K4" t="n">
-        <v>710</v>
-      </c>
       <c r="L4" t="n">
-        <v>0.05071312820950069</v>
+        <v>0.05328993652333702</v>
       </c>
       <c r="M4" t="n">
-        <v>14.79732388040597</v>
+        <v>14.79989708156156</v>
       </c>
       <c r="N4" t="n">
-        <v>309.1124721767728</v>
+        <v>308.7969213645736</v>
       </c>
       <c r="O4" t="n">
-        <v>17.58159469947971</v>
+        <v>17.5726185118944</v>
       </c>
       <c r="P4" t="n">
-        <v>207.1948231413849</v>
+        <v>207.3253666843669</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -38419,28 +38575,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.2876776073475324</v>
+        <v>-0.3003388588911062</v>
       </c>
       <c r="J5" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K5" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L5" t="n">
-        <v>0.03143204484817019</v>
+        <v>0.03424000577339026</v>
       </c>
       <c r="M5" t="n">
-        <v>10.78858980912223</v>
+        <v>10.80953044675025</v>
       </c>
       <c r="N5" t="n">
-        <v>150.5751326123991</v>
+        <v>150.9805175064405</v>
       </c>
       <c r="O5" t="n">
-        <v>12.27090594098085</v>
+        <v>12.28741297045234</v>
       </c>
       <c r="P5" t="n">
-        <v>197.2584728448008</v>
+        <v>197.3907274900762</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -38491,28 +38647,28 @@
         <v>0.1712</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2324633926203691</v>
+        <v>0.2202874241347678</v>
       </c>
       <c r="J6" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K6" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L6" t="n">
-        <v>0.01943002561494012</v>
+        <v>0.01753703409664142</v>
       </c>
       <c r="M6" t="n">
-        <v>10.42693102065901</v>
+        <v>10.45589726487064</v>
       </c>
       <c r="N6" t="n">
-        <v>161.1286392220799</v>
+        <v>161.4252776001884</v>
       </c>
       <c r="O6" t="n">
-        <v>12.69364562377885</v>
+        <v>12.70532477350297</v>
       </c>
       <c r="P6" t="n">
-        <v>195.5213166165802</v>
+        <v>195.6485220951779</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -38563,28 +38719,28 @@
         <v>0.1853</v>
       </c>
       <c r="I7" t="n">
-        <v>-0.006120099901009952</v>
+        <v>-0.01237770462085234</v>
       </c>
       <c r="J7" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K7" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L7" t="n">
-        <v>4.613708477851919e-05</v>
+        <v>0.000189430524062395</v>
       </c>
       <c r="M7" t="n">
-        <v>5.937877430986552</v>
+        <v>5.944713146881234</v>
       </c>
       <c r="N7" t="n">
-        <v>47.96287567294176</v>
+        <v>48.01534816736712</v>
       </c>
       <c r="O7" t="n">
-        <v>6.925523494505073</v>
+        <v>6.929310800315362</v>
       </c>
       <c r="P7" t="n">
-        <v>216.9764502245468</v>
+        <v>217.0418218616176</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -38635,28 +38791,28 @@
         <v>0.0536</v>
       </c>
       <c r="I8" t="n">
-        <v>0.09552498527015191</v>
+        <v>0.08293208273050579</v>
       </c>
       <c r="J8" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K8" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L8" t="n">
-        <v>0.002867931871854967</v>
+        <v>0.002171355640894657</v>
       </c>
       <c r="M8" t="n">
-        <v>11.11392676056879</v>
+        <v>11.13451586265315</v>
       </c>
       <c r="N8" t="n">
-        <v>186.5027047614997</v>
+        <v>186.7332075556033</v>
       </c>
       <c r="O8" t="n">
-        <v>13.65659931174301</v>
+        <v>13.66503595149326</v>
       </c>
       <c r="P8" t="n">
-        <v>177.5929026053269</v>
+        <v>177.7248765771225</v>
       </c>
       <c r="Q8" t="inlineStr"/>
       <c r="R8" t="inlineStr">
@@ -38707,28 +38863,28 @@
         <v>0.0254</v>
       </c>
       <c r="I9" t="n">
-        <v>-0.2305503770984938</v>
+        <v>-0.2338348245630526</v>
       </c>
       <c r="J9" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K9" t="n">
-        <v>712</v>
+        <v>715</v>
       </c>
       <c r="L9" t="n">
-        <v>0.05524406760976686</v>
+        <v>0.05716558708521879</v>
       </c>
       <c r="M9" t="n">
-        <v>5.707795302372983</v>
+        <v>5.701292519859201</v>
       </c>
       <c r="N9" t="n">
-        <v>53.4358812418188</v>
+        <v>53.2807764679775</v>
       </c>
       <c r="O9" t="n">
-        <v>7.309985037044795</v>
+        <v>7.299368223892908</v>
       </c>
       <c r="P9" t="n">
-        <v>208.179941553448</v>
+        <v>208.2143605948225</v>
       </c>
       <c r="Q9" t="inlineStr"/>
       <c r="R9" t="inlineStr">
@@ -38779,28 +38935,28 @@
         <v>0.2</v>
       </c>
       <c r="I10" t="n">
-        <v>2.454042014400553</v>
+        <v>2.465044084972295</v>
       </c>
       <c r="J10" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K10" t="n">
-        <v>709</v>
+        <v>712</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1301243142685252</v>
+        <v>0.1321556426714104</v>
       </c>
       <c r="M10" t="n">
-        <v>28.6068684976819</v>
+        <v>28.56222728761719</v>
       </c>
       <c r="N10" t="n">
-        <v>2359.044612168486</v>
+        <v>2349.947597395676</v>
       </c>
       <c r="O10" t="n">
-        <v>48.5699970369413</v>
+        <v>48.47625807955556</v>
       </c>
       <c r="P10" t="n">
-        <v>621.7723847348525</v>
+        <v>621.6566456647154</v>
       </c>
       <c r="Q10" t="inlineStr"/>
       <c r="R10" t="inlineStr">
@@ -38851,28 +39007,28 @@
         <v>0.2</v>
       </c>
       <c r="I11" t="n">
-        <v>0.652871181447758</v>
+        <v>0.5951743488483423</v>
       </c>
       <c r="J11" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="K11" t="n">
-        <v>713</v>
+        <v>716</v>
       </c>
       <c r="L11" t="n">
-        <v>0.00156868339271965</v>
+        <v>0.001314275223839423</v>
       </c>
       <c r="M11" t="n">
-        <v>101.1005077823664</v>
+        <v>101.0748934858959</v>
       </c>
       <c r="N11" t="n">
-        <v>16018.4898586241</v>
+        <v>15973.25434988038</v>
       </c>
       <c r="O11" t="n">
-        <v>126.564172887212</v>
+        <v>126.385340723837</v>
       </c>
       <c r="P11" t="n">
-        <v>679.9990847803964</v>
+        <v>680.6018563771306</v>
       </c>
       <c r="Q11" t="inlineStr"/>
       <c r="R11" t="inlineStr">
@@ -38910,7 +39066,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L714"/>
+  <dimension ref="A1:L717"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -83137,6 +83293,192 @@
         </is>
       </c>
     </row>
+    <row r="715">
+      <c r="A715" s="1" t="inlineStr">
+        <is>
+          <t>2026-08-28 22:13:37+00:00</t>
+        </is>
+      </c>
+      <c r="B715" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C715" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D715" t="inlineStr">
+        <is>
+          <t>-43.630299150859976,172.69585245718133</t>
+        </is>
+      </c>
+      <c r="E715" t="inlineStr">
+        <is>
+          <t>-43.63026574908144,172.69486077092813</t>
+        </is>
+      </c>
+      <c r="F715" t="inlineStr">
+        <is>
+          <t>-43.63039198010122,172.6938690942935</t>
+        </is>
+      </c>
+      <c r="G715" t="inlineStr">
+        <is>
+          <t>-43.630500477935435,172.69286880157054</t>
+        </is>
+      </c>
+      <c r="H715" t="inlineStr">
+        <is>
+          <t>-43.63021917346155,172.6917432718978</t>
+        </is>
+      </c>
+      <c r="I715" t="inlineStr">
+        <is>
+          <t>-43.630809583911976,172.69104969547593</t>
+        </is>
+      </c>
+      <c r="J715" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K715" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L715" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="716">
+      <c r="A716" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-13 22:13:40+00:00</t>
+        </is>
+      </c>
+      <c r="B716" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C716" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D716" t="inlineStr">
+        <is>
+          <t>-43.63026943756801,172.6958524546273</t>
+        </is>
+      </c>
+      <c r="E716" t="inlineStr">
+        <is>
+          <t>-43.63023459514632,172.6948607687624</t>
+        </is>
+      </c>
+      <c r="F716" t="inlineStr">
+        <is>
+          <t>-43.63034407867826,172.69386909175165</t>
+        </is>
+      </c>
+      <c r="G716" t="inlineStr">
+        <is>
+          <t>-43.63048402305669,172.69287145547136</t>
+        </is>
+      </c>
+      <c r="H716" t="inlineStr">
+        <is>
+          <t>-43.63020226719945,172.69173107019972</t>
+        </is>
+      </c>
+      <c r="I716" t="inlineStr">
+        <is>
+          <t>-43.63081357148228,172.6910525726203</t>
+        </is>
+      </c>
+      <c r="J716" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K716" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L716" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="717">
+      <c r="A717" s="1" t="inlineStr">
+        <is>
+          <t>2026-09-14 22:07:36+00:00</t>
+        </is>
+      </c>
+      <c r="B717" t="inlineStr">
+        <is>
+          <t>-43.63208548418465,172.6942787540965</t>
+        </is>
+      </c>
+      <c r="C717" t="inlineStr">
+        <is>
+          <t>-43.631391164824954,172.69401235486677</t>
+        </is>
+      </c>
+      <c r="D717" t="inlineStr">
+        <is>
+          <t>-43.63027565034726,172.69585245516132</t>
+        </is>
+      </c>
+      <c r="E717" t="inlineStr">
+        <is>
+          <t>-43.63024170832804,172.6948607692569</t>
+        </is>
+      </c>
+      <c r="F717" t="inlineStr">
+        <is>
+          <t>-43.63035533371188,172.6938690923489</t>
+        </is>
+      </c>
+      <c r="G717" t="inlineStr">
+        <is>
+          <t>-43.630489120491966,172.6928706333392</t>
+        </is>
+      </c>
+      <c r="H717" t="inlineStr">
+        <is>
+          <t>-43.63020864692115,172.69173567461328</t>
+        </is>
+      </c>
+      <c r="I717" t="inlineStr">
+        <is>
+          <t>-43.63080774962962,172.69104837198967</t>
+        </is>
+      </c>
+      <c r="J717" t="inlineStr">
+        <is>
+          <t>-43.63106840681668,172.69319266049993</t>
+        </is>
+      </c>
+      <c r="K717" t="inlineStr">
+        <is>
+          <t>-43.63177888963988,172.69335601238183</t>
+        </is>
+      </c>
+      <c r="L717" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
